--- a/demand_min.xlsx
+++ b/demand_min.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uzk-my.sharepoint.com/personal/linus_palm_uzk_onmicrosoft_com/Documents/Master/MA/master-thesis-nurse-scheduling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{7C85814F-0396-AB4C-876E-7801D68A3AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AADDFA0-8DF7-F74A-83E4-FDAF9C6BF002}"/>
+  <xr:revisionPtr revIDLastSave="163" documentId="13_ncr:1_{7C85814F-0396-AB4C-876E-7801D68A3AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A416EDF4-FA00-FD41-8C66-4BEB4FBBF3D6}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{F6C4B857-2221-7442-B2F7-99991C74024F}"/>
+    <workbookView xWindow="7600" yWindow="4100" windowWidth="28800" windowHeight="17500" xr2:uid="{F6C4B857-2221-7442-B2F7-99991C74024F}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -130,6 +130,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -449,10 +453,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5726D70-3220-EE45-8CC4-80523B43DD04}">
-  <dimension ref="A1:AF4"/>
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -546,11 +550,8 @@
       <c r="AE1" s="1">
         <v>29</v>
       </c>
-      <c r="AF1" s="1">
-        <v>30</v>
-      </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -644,11 +645,8 @@
       <c r="AE2" s="2">
         <v>3</v>
       </c>
-      <c r="AF2" s="2">
-        <v>3</v>
-      </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -742,106 +740,100 @@
       <c r="AE3" s="2">
         <v>3</v>
       </c>
-      <c r="AF3" s="2">
-        <v>3</v>
-      </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE4" s="2">
-        <v>2</v>
-      </c>
-      <c r="AF4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
